--- a/IPPU/A1_Outputs/A-O_Demand_COMPLETED.xlsx
+++ b/IPPU/A1_Outputs/A-O_Demand_COMPLETED.xlsx
@@ -749,82 +749,82 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.2149</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>0.252</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>0.2891</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>0.3318</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>0.3745</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>0.4237</v>
+        <v>0</v>
       </c>
       <c r="O3">
-        <v>0.4729</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>0.496</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>0.5191</v>
+        <v>0</v>
       </c>
       <c r="R3">
-        <v>0.8611</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>1.203</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>1.3251</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>1.9576</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>2.384</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>2.8103</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>3.2367</v>
+        <v>0</v>
       </c>
       <c r="Y3">
-        <v>3.6631</v>
+        <v>0</v>
       </c>
       <c r="Z3">
-        <v>4.0895</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>4.5159</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>4.9422</v>
+        <v>0</v>
       </c>
       <c r="AC3">
-        <v>5.3686</v>
+        <v>0</v>
       </c>
       <c r="AD3">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="AE3">
-        <v>5.3913</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>5.4026</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>5.414</v>
+        <v>0</v>
       </c>
       <c r="AH3">
-        <v>5.4253</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:34">
@@ -853,82 +853,82 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>0.0034</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>0.0026</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>0.0015</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>0.0011</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>0.0009</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>0.0007</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>0.0008</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>0.0011</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>0.0012</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>0.0013</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>0.0015</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>0.0016</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>0.0016</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>0.0016</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>0.0016</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>0.0016</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.0016</v>
       </c>
     </row>
     <row r="5" spans="1:34">
@@ -957,82 +957,82 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>0.0043</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>0.0038</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>0.0052</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>0.0069</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>0.0062</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>0.0055</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>0.0044</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>0.0232</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>0.0359</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.0479</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>0.0737</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>0.0898</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>0.1059</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>0.122</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>0.1381</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>0.1541</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>0.1702</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>0.1863</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>0.2023</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>0.2028</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>0.2032</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>0.2036</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>0.204</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>0.2045</v>
       </c>
     </row>
     <row r="6" spans="1:34">
@@ -1061,82 +1061,82 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>0.0091</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>0.0108</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>0.0126</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>0.0137</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>0.0101</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>0.0067</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>0.0063</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>0.0068</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>0.0954</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>0.1172</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>0.1854</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>0.2258</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>0.2662</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>0.3066</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>0.3469</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>0.3873</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>0.4277</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>0.4681</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>0.5085</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>0.5117</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>0.5128</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.5139</v>
       </c>
     </row>
     <row r="7" spans="1:34">
@@ -1165,82 +1165,82 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>0.0794</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>0.0906</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>0.1235</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>0.1658</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>0.2255</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>0.2765</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>0.3072</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>0.3382</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>0.3628</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>0.3978</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>0.427</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>0.4122</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>0.4691</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>0.5713</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>0.6735</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>0.8778</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.0822</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.1844</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>1.2865</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.2893</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.292</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.2947</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.2974</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>1.3001</v>
       </c>
     </row>
     <row r="8" spans="1:34">
@@ -1269,82 +1269,82 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>0.0078</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>0.0109</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>0.0125</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>0.0094</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>0.0063</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>0.0086</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>0.0039</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>0.0409</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>0.1464</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>0.1783</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>0.2101</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>0.242</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>0.2739</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>0.3058</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>0.3377</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>0.3696</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>0.4014</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>0.4023</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>0.4031</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>0.404</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>0.4048</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>0.4057</v>
       </c>
     </row>
     <row r="9" spans="1:34">
@@ -1382,73 +1382,73 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>0.0007</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>0.0014</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>0.0007</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>0.0014</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>0.0014</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>0.0007</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>0.0007</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>0.0007</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>0.0014</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>0.0022</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>0.0024</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>0.0029</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>0.0033</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>0.0038</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>0.0042</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>0.0046</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>0.0051</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>0.0055</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>0.0055</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>0.0055</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>0.0055</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>0.0056</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>0.0056</v>
       </c>
     </row>
     <row r="10" spans="1:34">
@@ -2682,13 +2682,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9464F164-7138-478C-96F9-9FB0EC68C62D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C4148F7-2F4F-4F8B-8C37-36DAD8BD7987}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32565E92-CB56-4922-93F8-353DFFB22787}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E597A9DA-2FAA-4B0F-A504-507F275EFCB3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D6E6029-4B0F-4B2A-B9D2-D9AD2CB15CA2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F08A8130-F2B2-409F-A97E-99516DB715F7}"/>
 </file>